--- a/lessons/qr/excels/remarks_leo.xlsx
+++ b/lessons/qr/excels/remarks_leo.xlsx
@@ -167,12 +167,12 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -&lt; (12:29:08.369), -id (12:31:25.626), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), +positioning (00:00:00), +positioning (00:00:00), +ID (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -&lt; (12:29:08.369), -id (12:31:25.626) ~0.00, -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), +positioning (00:00:00), +positioning (00:00:00), +ID (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-column (12:27:17.320), -280 (12:41:14.808), -mapContainer (12:50:07.768), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +f80 (00:00:00), +cplumn (00:00:00), +mapmarker (00:00:00)</t>
+        <t>-column (12:27:17.320) ~0.83, -280 (12:41:14.808) ~0.67, -mapContainer (12:50:07.768) ~0.50, -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +f80 (00:00:00), +cplumn (00:00:00), +mapmarker (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
@@ -202,7 +202,7 @@
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>-script (13:05:47.673), -src (13:05:48.559), -script (13:06:51.081), +SCRIPT (00:00:00), +SRC (00:00:00), +SCRIPT (00:00:00)</t>
+        <t>-script (13:05:47.673) ~0.00, -src (13:05:48.559) ~0.00, -script (13:06:51.081) ~0.00, +SCRIPT (00:00:00), +SRC (00:00:00), +SCRIPT (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
@@ -237,12 +237,12 @@
     </comment>
     <comment ref="M14" authorId="0" shapeId="0">
       <text>
-        <t>-123456 (12:24:02.680), -marker (12:35:44.425), -&gt; (12:35:45.158), -&lt; (12:49:02.019), -/ (12:49:02.029), -div (12:49:02.059), -&gt; (12:49:02.069), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:18.033), +654321 (00:00:00), +market (00:00:00)</t>
+        <t>-123456 (12:24:02.680) ~0.00, -marker (12:35:44.425) ~0.83, -&gt; (12:35:45.158), -&lt; (12:49:02.019), -/ (12:49:02.029), -div (12:49:02.059), -&gt; (12:49:02.069), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:18.033), +654321 (00:00:00), +market (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q14" authorId="0" shapeId="0">
       <text>
-        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -CANCEL (13:02:31.086), -SCAN (13:02:39.170), -facingMode (13:12:37.968), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapcontainer (00:00:00), +cancel (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00), +facingmode (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), +showMarKerAt (00:00:00)</t>
+        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525) ~0.92, -CANCEL (13:02:31.086), -SCAN (13:02:39.170), -facingMode (13:12:37.968) ~0.90, -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930) ~0.92, -toggleScanner (13:20:36.733) ~0.92, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapcontainer (00:00:00), +cancel (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00), +facingmode (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), +showMarKerAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D19" authorId="0" shapeId="0">
@@ -267,7 +267,7 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-QR (12:19:38.447), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:07:18.033), +Document (00:00:00), +Positionaning (00:00:00), +Btn (00:00:00)</t>
+        <t>-QR (12:19:38.447), -Positioning (12:19:41.715) ~0.18, -Positioning (12:21:32.906) ~0.85, -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502) ~0.67, -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:07:18.033), +Document (00:00:00), +Positionaning (00:00:00), +Btn (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
@@ -277,7 +277,7 @@
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>-camera (13:10:05.606), -} (13:12:17.001), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -const (13:19:51.277), +camere (00:00:00), +console (00:00:00)</t>
+        <t>-camera (13:10:05.606) ~0.83, -} (13:12:17.001), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -const (13:19:51.277) ~0.57, +camere (00:00:00), +console (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D21" authorId="0" shapeId="0">
@@ -302,7 +302,7 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378), +&lt; (00:00:00), +div (00:00:00), +Scan (00:00:00)</t>
+        <t>-/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378) ~0.25, +&lt; (00:00:00), +div (00:00:00), +Scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
@@ -312,7 +312,7 @@
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -CANCEL (13:02:31.086), -SCAN (13:02:39.170), +Cancel (00:00:00), +Scan (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -CANCEL (13:02:31.086), -SCAN (13:02:39.170), +Cancel (00:00:00), +Scan (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -332,12 +332,12 @@
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>-onclick (12:59:42.303), +onClick (00:00:00)</t>
+        <t>-onclick (12:59:42.303) ~0.86, +onClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-3vw (12:36:23.573), -height (12:37:16.574), -: (12:37:16.693), -; (12:37:19.456), -; (12:42:02.654), -0 (12:44:06.443), -0 (12:44:08.691), -; (12:45:38.251), +59 (00:00:00), +% (00:00:00), +56 (00:00:00), +% (00:00:00)</t>
+        <t>-3vw (12:36:23.573), -height (12:37:16.574), -: (12:37:16.693), -; (12:37:19.456), -; (12:42:02.654), -0 (12:44:06.443) ~0.00, -0 (12:44:08.691) ~0.00, -; (12:45:38.251), +59 (00:00:00), +% (00:00:00), +56 (00:00:00), +% (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
@@ -367,12 +367,12 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909), -SCAN (13:00:21.378), -script (13:05:47.673), -src (13:05:48.559), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +positioning (00:00:00), +H1 (00:00:00), +positioning (00:00:00), +H1 (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909) ~0.92, -SCAN (13:00:21.378), -script (13:05:47.673), -src (13:05:48.559), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +positioning (00:00:00), +H1 (00:00:00), +positioning (00:00:00), +H1 (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (12:50:07.768), +mapcontainer (00:00:00)</t>
+        <t>-mapContainer (12:50:07.768) ~0.92, +mapcontainer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
@@ -392,7 +392,7 @@
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
-        <t>-qrcode (13:05:55.667), +sqrcode (00:00:00)</t>
+        <t>-qrcode (13:05:55.667) ~0.86, +sqrcode (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D31" authorId="0" shapeId="0">
@@ -417,12 +417,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-meta (12:19:34.574), -charset (12:19:34.654), -= (12:19:34.664), -" (12:19:34.674), -UTF (12:19:34.704), -- (12:19:34.714), -8 (12:19:34.724), -" (12:19:34.734), -&gt; (12:19:34.744), -&lt; (12:19:34.764), -meta (12:19:34.804), -name (12:19:34.854), -= (12:19:34.864), -" (12:19:34.874), -viewport (12:19:34.954), -" (12:19:34.964), -content (12:19:35.044), -= (12:19:35.054), -" (12:19:35.064), -width (12:19:35.114), -= (12:19:35.124), -device (12:19:35.184), -- (12:19:35.194), -width (12:19:35.244), -, (12:19:35.254), -initial (12:19:35.334), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.534), -&lt; (12:19:35.624), -QR (12:19:38.447), -Positioning (12:19:41.715), +Qr (00:00:00), +Positionining (00:00:00)</t>
+        <t>-meta (12:19:34.574), -charset (12:19:34.654), -= (12:19:34.664), -" (12:19:34.674), -UTF (12:19:34.704), -- (12:19:34.714), -8 (12:19:34.724), -" (12:19:34.734), -&gt; (12:19:34.744), -&lt; (12:19:34.764), -meta (12:19:34.804), -name (12:19:34.854), -= (12:19:34.864), -" (12:19:34.874), -viewport (12:19:34.954), -" (12:19:34.964), -content (12:19:35.044), -= (12:19:35.054), -" (12:19:35.064), -width (12:19:35.114), -= (12:19:35.124), -device (12:19:35.184), -- (12:19:35.194), -width (12:19:35.244), -, (12:19:35.254), -initial (12:19:35.334), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.534), -&lt; (12:19:35.624), -QR (12:19:38.447) ~0.50, -Positioning (12:19:41.715) ~0.85, +Qr (00:00:00), +Positionining (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:27:22.424), -: (12:35:35.579), -camera (13:08:26.947), +; (00:00:00), +: (00:00:00), +camer (00:00:00)</t>
+        <t>-; (12:27:22.424) ~1.00, -: (12:35:35.579), -camera (13:08:26.947) ~0.83, +; (00:00:00), +: (00:00:00), +camer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
@@ -447,12 +447,12 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -0 (12:19:35.434), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -: (13:05:50.571), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), +positioning (00:00:00), +positioning (00:00:00)</t>
+        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -0 (12:19:35.434), -Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -: (13:05:50.571), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), +positioning (00:00:00), +positioning (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-; (13:02:33.763), -" (13:02:39.256), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -none (13:23:57.811), -" (13:23:57.954), -. (13:24:12.217), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
+        <t>-; (13:02:33.763), -" (13:02:39.256), -; (13:11:40.424), -startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -none (13:23:57.811), -" (13:23:57.954), -. (13:24:12.217), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D41" authorId="0" shapeId="0">
@@ -477,17 +477,17 @@
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:19:34.294), -&lt; (12:19:35.624), -&lt; (12:21:30.346), -marker (12:35:44.425), -mapContainer (12:49:01.909), -script (12:52:45.286), -script (12:53:08.182), -SCAN (13:00:21.378), -script (13:05:47.673), -https (13:05:50.422), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +scan (00:00:00), +srcipt (00:00:00), +http (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
+        <t>-&lt; (12:19:34.294) ~0.00, -&lt; (12:19:35.624) ~0.00, -&lt; (12:21:30.346), -marker (12:35:44.425) ~0.83, -mapContainer (12:49:01.909) ~0.75, -script (12:52:45.286) ~0.67, -script (12:53:08.182) ~0.83, -SCAN (13:00:21.378) ~0.00, -script (13:05:47.673) ~0.67, -https (13:05:50.422) ~0.80, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081) ~0.83, +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +scan (00:00:00), +srcipt (00:00:00), +http (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-items (12:27:20.468), -} (12:27:40.523), -marker (12:36:09.957), -} (12:36:17.541), -; (12:38:00.710), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +market (00:00:00)</t>
+        <t>-items (12:27:20.468) ~0.80, -} (12:27:40.523), -marker (12:36:09.957) ~0.83, -} (12:36:17.541), -; (12:38:00.710), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +market (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q41" authorId="0" shapeId="0">
       <text>
-        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -. (13:14:34.576), -( (13:14:36.285), -function (13:14:37.982), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
+        <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574) ~0.89, -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738) ~0.86, -startScanner (13:11:29.686) ~0.85, -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -. (13:14:34.576), -( (13:14:36.285), -function (13:14:37.982), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075) ~0.00, +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D42" authorId="0" shapeId="0">
@@ -512,17 +512,17 @@
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -script (12:52:45.286), -SCAN (13:00:21.378), -https (13:05:50.422), +positioning (00:00:00), +SCAn (00:00:00), +http (00:00:00), +srcipt (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -script (12:52:45.286) ~0.67, -SCAN (13:00:21.378) ~0.75, -https (13:05:50.422) ~0.80, +positioning (00:00:00), +SCAn (00:00:00), +http (00:00:00), +srcipt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Arial (12:27:44.328), -marker (12:36:09.957), -border (12:38:55.775), -; (12:42:02.654), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
+        <t>-Arial (12:27:44.328) ~0.83, -marker (12:36:09.957) ~0.83, -border (12:38:55.775) ~0.83, -; (12:42:02.654), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (13:20:05.930), +showMarketAt (00:00:00)</t>
+        <t>-showMarkerAt (13:20:05.930) ~0.92, +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -552,7 +552,7 @@
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
       <text>
-        <t>-environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
+        <t>-environment (13:12:42.232) ~0.91, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D46" authorId="0" shapeId="0">
@@ -577,7 +577,7 @@
     </comment>
     <comment ref="M46" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -onclick (12:59:42.303), +positioning (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +onClick (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -onclick (12:59:42.303) ~0.86, +positioning (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +onClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
@@ -587,7 +587,7 @@
     </comment>
     <comment ref="Q46" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -CANCEL (13:02:31.086), +( (00:00:00), +) (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innerText (00:00:00), +CANCEl (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -CANCEL (13:02:31.086) ~0.00, +( (00:00:00), +) (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innerText (00:00:00), +CANCEl (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D48" authorId="0" shapeId="0">
@@ -612,17 +612,17 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:19:34.144), -viewport (12:19:34.954), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -&gt; (12:19:35.534), -/ (12:19:35.634), -title (12:19:35.684), -QR (12:19:38.447), -/ (12:21:30.356), -QR (12:21:30.856), -stylesheet (12:23:47.522), -href (12:23:59.034), -toggleScanner (12:59:48.978), -&gt; (13:06:51.091), +veiwport (00:00:00), +OR (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +OR (00:00:00), +togglescanner (00:00:00)</t>
+        <t>-! (12:19:34.144), -viewport (12:19:34.954) ~0.75, -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -&gt; (12:19:35.534), -/ (12:19:35.634), -title (12:19:35.684), -QR (12:19:38.447), -/ (12:21:30.356), -QR (12:21:30.856) ~0.50, -stylesheet (12:23:47.522) ~0.80, -href (12:23:59.034) ~0.50, -toggleScanner (12:59:48.978) ~0.92, -&gt; (13:06:51.091) ~0.00, +veiwport (00:00:00), +OR (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +OR (00:00:00), +togglescanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-# (12:41:14.043), -280 (12:41:14.808), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +green (00:00:00), +lime (00:00:00), +; (00:00:00)</t>
+        <t>-# (12:41:14.043), -280 (12:41:14.808) ~0.00, -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855) ~0.40, -) (12:42:30.228), -; (12:42:31.537) ~1.00, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +green (00:00:00), +lime (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-scannerOn (13:00:41.475), -CANCEL (13:02:31.086), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), +scannerON (00:00:00), +CANCLE (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
+        <t>-scannerOn (13:00:41.475) ~0.89, -CANCEL (13:02:31.086), -start (13:12:21.297) ~0.60, -environment (13:12:42.232) ~0.91, -showMarkerAt (13:20:05.930) ~0.92, +scannerON (00:00:00), +CANCLE (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -642,17 +642,17 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:19:34.954), -png (12:30:36.357), +viewpoint (00:00:00), +PNG (00:00:00)</t>
+        <t>-viewport (12:19:34.954) ~0.78, -png (12:30:36.357) ~0.00, +viewpoint (00:00:00), +PNG (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:27:22.424), -} (12:32:35.009), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -# (12:36:08.726), -marker (12:36:09.957), -{ (12:36:10.360), -} (12:36:17.541), -width (12:36:18.827), -: (12:36:19.115), -3vw (12:36:23.573), -; (12:36:25.789), -height (12:37:16.574), -: (12:37:16.693), -3vw (12:37:18.454), -; (12:37:19.456), -background (12:37:29.322), -- (12:37:29.578), -color (12:37:30.642), -: (12:37:30.747), -black (12:37:31.976), -; (12:37:32.154), -border (12:37:58.210), -- (12:37:58.480), -radius (12:37:59.488), -: (12:37:59.684), -50 (12:38:00.274), -% (12:38:00.472), -; (12:38:00.710), -outline (12:38:33.154), -: (12:38:33.436), -5px (12:38:34.274), -solid (12:38:36.469), -border (12:38:55.775), -: (12:38:55.983), -5px (12:38:56.840), -solid (12:38:57.986), -white (12:38:59.153), -; (12:38:59.359), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -var (12:41:59.152), -( (12:41:59.354), -- (12:42:00.527), -theme (12:42:01.928), -) (12:42:02.226), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -position (12:44:00.909), -: (12:44:01.045), -absolute (12:44:03.220), -; (12:44:03.644), -top (12:44:05.651), -: (12:44:05.880), -0 (12:44:06.443), -; (12:44:06.772), -left (12:44:08.033), -: (12:44:08.227), -0 (12:44:08.691), -; (12:44:08.978), -transform (12:45:33.046), -: (12:45:33.314), -translate (12:45:34.855), -( (12:45:35.069), -- (12:45:35.321), -50 (12:45:35.855), -% (12:45:36.123), -, (12:45:36.383), -- (12:45:36.755), -50 (12:45:37.279), -% (12:45:37.687), -) (12:45:37.895), -; (12:45:38.251), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +# (00:00:00), +280 (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+        <t>-; (12:27:22.424), -} (12:32:35.009), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -# (12:36:08.726), -marker (12:36:09.957), -{ (12:36:10.360), -} (12:36:17.541), -width (12:36:18.827), -: (12:36:19.115), -3vw (12:36:23.573), -; (12:36:25.789), -height (12:37:16.574), -: (12:37:16.693), -3vw (12:37:18.454), -; (12:37:19.456), -background (12:37:29.322) ~1.00, -- (12:37:29.578), -color (12:37:30.642), -: (12:37:30.747), -black (12:37:31.976), -; (12:37:32.154), -border (12:37:58.210), -- (12:37:58.480), -radius (12:37:59.488), -: (12:37:59.684), -50 (12:38:00.274), -% (12:38:00.472), -; (12:38:00.710), -outline (12:38:33.154), -: (12:38:33.436), -5px (12:38:34.274), -solid (12:38:36.469), -border (12:38:55.775), -: (12:38:55.983), -5px (12:38:56.840), -solid (12:38:57.986), -white (12:38:59.153), -; (12:38:59.359), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -var (12:41:59.152), -( (12:41:59.354), -- (12:42:00.527), -theme (12:42:01.928), -) (12:42:02.226) ~0.00, -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -position (12:44:00.909), -: (12:44:01.045), -absolute (12:44:03.220), -; (12:44:03.644), -top (12:44:05.651), -: (12:44:05.880), -0 (12:44:06.443), -; (12:44:06.772), -left (12:44:08.033), -: (12:44:08.227), -0 (12:44:08.691), -; (12:44:08.978), -transform (12:45:33.046), -: (12:45:33.314), -translate (12:45:34.855), -( (12:45:35.069), -- (12:45:35.321), -50 (12:45:35.855), -% (12:45:36.123), -, (12:45:36.383), -- (12:45:36.755), -50 (12:45:37.279), -% (12:45:37.687), -) (12:45:37.895), -; (12:45:38.251), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754) ~1.00, -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490) ~0.00, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +# (00:00:00), +280 (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (12:56:12.525), -= (12:57:18.822), -" (13:02:31.386), -; (13:02:33.763), -" (13:02:39.256), -; (13:02:39.352), -, (13:13:22.080), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +; (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
+        <t>-showMarkerAt (12:56:12.525) ~0.92, -= (12:57:18.822), -" (13:02:31.386), -; (13:02:33.763), -" (13:02:39.256), -; (13:02:39.352), -, (13:13:22.080) ~0.00, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +; (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -667,7 +667,7 @@
     </comment>
     <comment ref="M51" authorId="0" shapeId="0">
       <text>
-        <t>-/ (12:24:11.601), -onclick (12:59:42.303), +onClick (00:00:00)</t>
+        <t>-/ (12:24:11.601), -onclick (12:59:42.303) ~0.86, +onClick (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
@@ -727,7 +727,7 @@
     </comment>
     <comment ref="M59" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -/ (12:24:11.601), +positioning (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -/ (12:24:11.601), +positioning (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
@@ -737,7 +737,7 @@
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-startScanner (13:11:29.686), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +console (00:00:00), +log (00:00:00)</t>
+        <t>-startScanner (13:11:29.686) ~0.92, -const (13:19:51.277) ~0.57, -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262) ~0.00, -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +console (00:00:00), +log (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -762,22 +762,22 @@
     </comment>
     <comment ref="M61" authorId="0" shapeId="0">
       <text>
-        <t>-/ (12:19:35.634), -&gt; (12:19:35.694), -QR (12:19:38.447), -Positioning (12:19:41.715), -&gt; (12:21:30.386), -QR (12:21:30.856), -Positioning (12:21:32.906), -&lt; (12:23:38.378), -link (12:23:39.280), -rel (12:23:45.117), -= (12:23:45.277), -" (12:23:45.703), -" (12:23:45.713), -stylesheet (12:23:47.522), -href (12:23:59.034), -= (12:23:59.297), -" (12:24:00.025), -" (12:24:00.035), -123456 (12:24:02.680), -. (12:24:02.918), -css (12:24:03.855), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -" (12:52:47.097), -&lt; (12:59:27.700), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), +OR (00:00:00), +positioning (00:00:00), +OR (00:00:00), +positioning (00:00:00), +body (00:00:00)</t>
+        <t>-/ (12:19:35.634), -&gt; (12:19:35.694), -QR (12:19:38.447) ~0.50, -Positioning (12:19:41.715) ~0.91, -&gt; (12:21:30.386), -QR (12:21:30.856) ~0.50, -Positioning (12:21:32.906) ~0.91, -&lt; (12:23:38.378), -link (12:23:39.280), -rel (12:23:45.117), -= (12:23:45.277), -" (12:23:45.703), -" (12:23:45.713), -stylesheet (12:23:47.522), -href (12:23:59.034), -= (12:23:59.297), -" (12:24:00.025), -" (12:24:00.035), -123456 (12:24:02.680), -. (12:24:02.918), -css (12:24:03.855), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -" (12:52:47.097), -&lt; (12:59:27.700), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), +OR (00:00:00), +positioning (00:00:00), +OR (00:00:00), +positioning (00:00:00), +body (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-mapContainer (12:50:07.768), -none (13:24:50.402), +body (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +0 (00:00:00), +; (00:00:00), +column (00:00:00), +align (00:00:00), +mapcontainer (00:00:00)</t>
+        <t>-mapContainer (12:50:07.768) ~0.92, -none (13:24:50.402), +body (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +0 (00:00:00), +; (00:00:00), +column (00:00:00), +align (00:00:00), +mapcontainer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q61" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (12:56:12.525), -scannerOn (13:00:41.475), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -= (13:02:30.040), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -) (13:12:35.212), -facingMode (13:12:37.968), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancel (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +showMarkeAT (00:00:00)</t>
+        <t>-showMarkerAt (12:56:12.525) ~0.83, -scannerOn (13:00:41.475) ~0.89, -scannerOn (13:02:03.160) ~0.89, -scannerOn (13:02:05.438) ~0.89, -scannerOn (13:02:26.202) ~0.89, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -= (13:02:30.040), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -} (13:02:36.228), -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420) ~0.36, -) (13:12:35.212), -facingMode (13:12:37.968) ~0.80, -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -" (13:23:57.165), -none (13:23:57.811) ~0.33, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancel (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +showMarkeAT (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -797,7 +797,7 @@
     </comment>
     <comment ref="Q62" authorId="0" shapeId="0">
       <text>
-        <t>-stopScanner (13:15:09.792), +stopSCanner (00:00:00)</t>
+        <t>-stopScanner (13:15:09.792) ~0.91, +stopSCanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D68" authorId="0" shapeId="0">
@@ -822,7 +822,7 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -mapContainer (12:49:01.909), -toggleScanner (12:59:48.978), -SCAN (13:00:21.378), -https (13:05:50.422), -: (13:05:50.571), -html5 (13:05:54.075), -type (13:05:57.063), -text (13:06:02.121), -javascript (13:06:04.645), +positioning (00:00:00), +positioning (00:00:00), +mapcontainer (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +togglescanner (00:00:00), +scan (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), +123456 (00:00:00), +js (00:00:00), +&gt; (00:00:00), +script (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
+        <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -mapContainer (12:49:01.909) ~0.92, -toggleScanner (12:59:48.978) ~0.92, -SCAN (13:00:21.378) ~0.00, -https (13:05:50.422) ~0.80, -: (13:05:50.571) ~0.00, -html5 (13:05:54.075) ~0.83, -type (13:05:57.063), -text (13:06:02.121), -javascript (13:06:04.645) ~0.20, +positioning (00:00:00), +positioning (00:00:00), +mapcontainer (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +togglescanner (00:00:00), +scan (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), +123456 (00:00:00), +js (00:00:00), +&gt; (00:00:00), +script (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
@@ -832,7 +832,7 @@
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -scannerOn (13:00:41.475), -toggleScanner (13:02:00.332), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -startScanner (13:12:06.965), -; (13:14:52.031), -stopScanner (13:15:09.792), -toggleScanner (13:20:36.733), -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075), +scanneron (00:00:00), +togglescanner (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +mapcantainer (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancle (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +startscanner (00:00:00), +togglescanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -scannerOn (13:00:41.475) ~0.89, -toggleScanner (13:02:00.332) ~0.92, -scannerOn (13:02:03.160) ~0.89, -scannerOn (13:02:05.438) ~0.89, -scannerOn (13:02:26.202) ~0.89, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574), -CANCEL (13:02:31.086), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -startScanner (13:12:06.965) ~0.92, -; (13:14:52.031), -stopScanner (13:15:09.792) ~0.91, -toggleScanner (13:20:36.733) ~0.92, -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088) ~0.92, -block (13:24:16.075) ~0.00, +scanneron (00:00:00), +togglescanner (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +mapcantainer (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancle (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +startscanner (00:00:00), +togglescanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D70" authorId="0" shapeId="0">
@@ -857,7 +857,7 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -Positioning (12:19:41.715), -html5 (13:05:54.075), +positioning (00:00:00), +html15 (00:00:00)</t>
+        <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -Positioning (12:19:41.715) ~0.91, -html5 (13:05:54.075) ~0.83, +positioning (00:00:00), +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
@@ -867,7 +867,7 @@
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-showMarkerAt (12:56:12.525), -startScanner (13:11:29.686), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), +StartScanner (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
+        <t>-showMarkerAt (12:56:12.525) ~0.92, -startScanner (13:11:29.686) ~0.92, -startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, +StartScanner (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D71" authorId="0" shapeId="0">
@@ -897,17 +897,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -marker (12:35:44.425), -toggleScanner (12:59:48.978), -html5 (13:05:54.075), +maker (00:00:00), +toggScanner (00:00:00), +html15 (00:00:00)</t>
+        <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -marker (12:35:44.425) ~0.83, -toggleScanner (12:59:48.978) ~0.85, -html5 (13:05:54.075) ~0.83, +maker (00:00:00), +toggScanner (00:00:00), +html15 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:32:37.955), -marker (12:36:09.957), -# (12:41:14.043), -280 (12:41:14.808), +green (00:00:00), +maker (00:00:00)</t>
+        <t>-; (12:32:37.955), -marker (12:36:09.957) ~0.83, -# (12:41:14.043), -280 (12:41:14.808) ~0.00, +green (00:00:00), +maker (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-marker (12:56:29.330), -marker (12:57:07.602), -left (12:57:18.355), -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612), -showMarkerAt (13:20:05.930), +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +maker (00:00:00), +maker (00:00:00), +top (00:00:00)</t>
+        <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -left (12:57:18.355) ~0.00, -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612) ~0.64, -showMarkerAt (13:20:05.930) ~0.92, +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +maker (00:00:00), +maker (00:00:00), +top (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D73" authorId="0" shapeId="0">
@@ -937,7 +937,7 @@
     </comment>
     <comment ref="Q73" authorId="0" shapeId="0">
       <text>
-        <t>-Html5Qrcode (13:09:48.612), +HTML5Qrcode (00:00:00)</t>
+        <t>-Html5Qrcode (13:09:48.612) ~0.73, +HTML5Qrcode (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D78" authorId="0" shapeId="0">
@@ -957,7 +957,7 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-onclick (12:59:42.303), -toggleScanner (12:59:48.978), +" (00:00:00), +" (00:00:00), +onClick (00:00:00), +toogleScanner (00:00:00)</t>
+        <t>-onclick (12:59:42.303) ~0.86, -toggleScanner (12:59:48.978) ~0.92, +" (00:00:00), +" (00:00:00), +onClick (00:00:00), +toogleScanner (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
@@ -987,7 +987,7 @@
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-error (13:14:54.485), +log (00:00:00)</t>
+        <t>-error (13:14:54.485) ~0.20, +log (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -1022,12 +1022,12 @@
     </comment>
     <comment ref="M82" authorId="0" shapeId="0">
       <text>
-        <t>-Positioning (12:21:32.906), -/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378), +Postitioning (00:00:00), +Scan (00:00:00)</t>
+        <t>-Positioning (12:21:32.906) ~0.92, -/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378) ~0.25, +Postitioning (00:00:00), +Scan (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-3vw (12:37:18.454), +3vh (00:00:00)</t>
+        <t>-3vw (12:37:18.454) ~0.67, +3vh (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -1057,7 +1057,7 @@
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-" (13:02:30.222), -CANCEL (13:02:31.086), -; (13:02:33.763), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -block (13:24:16.075), +Html5QRcode (00:00:00), +CANCLE (00:00:00), +SCANS (00:00:00)</t>
+        <t>-" (13:02:30.222), -CANCEL (13:02:31.086), -; (13:02:33.763), -SCAN (13:02:39.170) ~0.80, -" (13:02:39.256), -; (13:02:39.352), -Html5Qrcode (13:09:48.612) ~0.91, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -block (13:24:16.075), +Html5QRcode (00:00:00), +CANCLE (00:00:00), +SCANS (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -&lt; (12:29:08.369), -id (12:31:25.626), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), +positioning (00:00:00), +positioning (00:00:00), +ID (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -&lt; (12:29:08.369), -id (12:31:25.626) ~0.00, -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), +positioning (00:00:00), +positioning (00:00:00), +ID (00:00:00)</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-column (12:27:17.320), -280 (12:41:14.808), -mapContainer (12:50:07.768), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +f80 (00:00:00), +cplumn (00:00:00), +mapmarker (00:00:00)</t>
+          <t>-column (12:27:17.320) ~0.83, -280 (12:41:14.808) ~0.67, -mapContainer (12:50:07.768) ~0.50, -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +f80 (00:00:00), +cplumn (00:00:00), +mapmarker (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-script (13:05:47.673), -src (13:05:48.559), -script (13:06:51.081), +SCRIPT (00:00:00), +SRC (00:00:00), +SCRIPT (00:00:00)</t>
+          <t>-script (13:05:47.673) ~0.00, -src (13:05:48.559) ~0.00, -script (13:06:51.081) ~0.00, +SCRIPT (00:00:00), +SRC (00:00:00), +SCRIPT (00:00:00)</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-123456 (12:24:02.680), -marker (12:35:44.425), -&gt; (12:35:45.158), -&lt; (12:49:02.019), -/ (12:49:02.029), -div (12:49:02.059), -&gt; (12:49:02.069), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:18.033), +654321 (00:00:00), +market (00:00:00)</t>
+          <t>-123456 (12:24:02.680) ~0.00, -marker (12:35:44.425) ~0.83, -&gt; (12:35:45.158), -&lt; (12:49:02.019), -/ (12:49:02.029), -div (12:49:02.059), -&gt; (12:49:02.069), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:18.033), +654321 (00:00:00), +market (00:00:00)</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -CANCEL (13:02:31.086), -SCAN (13:02:39.170), -facingMode (13:12:37.968), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapcontainer (00:00:00), +cancel (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00), +facingmode (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), +showMarKerAt (00:00:00)</t>
+          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525) ~0.92, -CANCEL (13:02:31.086), -SCAN (13:02:39.170), -facingMode (13:12:37.968) ~0.90, -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930) ~0.92, -toggleScanner (13:20:36.733) ~0.92, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapcontainer (00:00:00), +cancel (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00), +facingmode (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), +showMarKerAt (00:00:00)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-QR (12:19:38.447), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:07:18.033), +Document (00:00:00), +Positionaning (00:00:00), +Btn (00:00:00)</t>
+          <t>-QR (12:19:38.447), -Positioning (12:19:41.715) ~0.18, -Positioning (12:21:32.906) ~0.85, -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -btn (12:59:30.502) ~0.67, -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:07:18.033), +Document (00:00:00), +Positionaning (00:00:00), +Btn (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-camera (13:10:05.606), -} (13:12:17.001), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -const (13:19:51.277), +camere (00:00:00), +console (00:00:00)</t>
+          <t>-camera (13:10:05.606) ~0.83, -} (13:12:17.001), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -const (13:19:51.277) ~0.57, +camere (00:00:00), +console (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378), +&lt; (00:00:00), +div (00:00:00), +Scan (00:00:00)</t>
+          <t>-/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378) ~0.25, +&lt; (00:00:00), +div (00:00:00), +Scan (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -CANCEL (13:02:31.086), -SCAN (13:02:39.170), +Cancel (00:00:00), +Scan (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -CANCEL (13:02:31.086), -SCAN (13:02:39.170), +Cancel (00:00:00), +Scan (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-onclick (12:59:42.303), +onClick (00:00:00)</t>
+          <t>-onclick (12:59:42.303) ~0.86, +onClick (00:00:00)</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-3vw (12:36:23.573), -height (12:37:16.574), -: (12:37:16.693), -; (12:37:19.456), -; (12:42:02.654), -0 (12:44:06.443), -0 (12:44:08.691), -; (12:45:38.251), +59 (00:00:00), +% (00:00:00), +56 (00:00:00), +% (00:00:00)</t>
+          <t>-3vw (12:36:23.573), -height (12:37:16.574), -: (12:37:16.693), -; (12:37:19.456), -; (12:42:02.654), -0 (12:44:06.443) ~0.00, -0 (12:44:08.691) ~0.00, -; (12:45:38.251), +59 (00:00:00), +% (00:00:00), +56 (00:00:00), +% (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909), -SCAN (13:00:21.378), -script (13:05:47.673), -src (13:05:48.559), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +positioning (00:00:00), +H1 (00:00:00), +positioning (00:00:00), +H1 (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -" (12:31:26.525), -map (12:31:27.486), -mapContainer (12:49:01.909) ~0.92, -SCAN (13:00:21.378), -script (13:05:47.673), -src (13:05:48.559), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +positioning (00:00:00), +H1 (00:00:00), +positioning (00:00:00), +H1 (00:00:00), +mapcontainer (00:00:00), +scan (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-mapContainer (12:50:07.768), +mapcontainer (00:00:00)</t>
+          <t>-mapContainer (12:50:07.768) ~0.92, +mapcontainer (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-qrcode (13:05:55.667), +sqrcode (00:00:00)</t>
+          <t>-qrcode (13:05:55.667) ~0.86, +sqrcode (00:00:00)</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-meta (12:19:34.574), -charset (12:19:34.654), -= (12:19:34.664), -" (12:19:34.674), -UTF (12:19:34.704), -- (12:19:34.714), -8 (12:19:34.724), -" (12:19:34.734), -&gt; (12:19:34.744), -&lt; (12:19:34.764), -meta (12:19:34.804), -name (12:19:34.854), -= (12:19:34.864), -" (12:19:34.874), -viewport (12:19:34.954), -" (12:19:34.964), -content (12:19:35.044), -= (12:19:35.054), -" (12:19:35.064), -width (12:19:35.114), -= (12:19:35.124), -device (12:19:35.184), -- (12:19:35.194), -width (12:19:35.244), -, (12:19:35.254), -initial (12:19:35.334), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.534), -&lt; (12:19:35.624), -QR (12:19:38.447), -Positioning (12:19:41.715), +Qr (00:00:00), +Positionining (00:00:00)</t>
+          <t>-meta (12:19:34.574), -charset (12:19:34.654), -= (12:19:34.664), -" (12:19:34.674), -UTF (12:19:34.704), -- (12:19:34.714), -8 (12:19:34.724), -" (12:19:34.734), -&gt; (12:19:34.744), -&lt; (12:19:34.764), -meta (12:19:34.804), -name (12:19:34.854), -= (12:19:34.864), -" (12:19:34.874), -viewport (12:19:34.954), -" (12:19:34.964), -content (12:19:35.044), -= (12:19:35.054), -" (12:19:35.064), -width (12:19:35.114), -= (12:19:35.124), -device (12:19:35.184), -- (12:19:35.194), -width (12:19:35.244), -, (12:19:35.254), -initial (12:19:35.334), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.534), -&lt; (12:19:35.624), -QR (12:19:38.447) ~0.50, -Positioning (12:19:41.715) ~0.85, +Qr (00:00:00), +Positionining (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-; (12:27:22.424), -: (12:35:35.579), -camera (13:08:26.947), +; (00:00:00), +: (00:00:00), +camer (00:00:00)</t>
+          <t>-; (12:27:22.424) ~1.00, -: (12:35:35.579), -camera (13:08:26.947) ~0.83, +; (00:00:00), +: (00:00:00), +camer (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -0 (12:19:35.434), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -: (13:05:50.571), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), +positioning (00:00:00), +positioning (00:00:00)</t>
+          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -0 (12:19:35.434), -Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -: (13:05:50.571), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), +positioning (00:00:00), +positioning (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-; (13:02:33.763), -" (13:02:39.256), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -none (13:23:57.811), -" (13:23:57.954), -. (13:24:12.217), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
+          <t>-; (13:02:33.763), -" (13:02:39.256), -; (13:11:40.424), -startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -none (13:23:57.811), -" (13:23:57.954), -. (13:24:12.217), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-&lt; (12:19:34.294), -&lt; (12:19:35.624), -&lt; (12:21:30.346), -marker (12:35:44.425), -mapContainer (12:49:01.909), -script (12:52:45.286), -script (12:53:08.182), -SCAN (13:00:21.378), -script (13:05:47.673), -https (13:05:50.422), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +scan (00:00:00), +srcipt (00:00:00), +http (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
+          <t>-&lt; (12:19:34.294) ~0.00, -&lt; (12:19:35.624) ~0.00, -&lt; (12:21:30.346), -marker (12:35:44.425) ~0.83, -mapContainer (12:49:01.909) ~0.75, -script (12:52:45.286) ~0.67, -script (12:53:08.182) ~0.83, -SCAN (13:00:21.378) ~0.00, -script (13:05:47.673) ~0.67, -https (13:05:50.422) ~0.80, -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081) ~0.83, +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +map (00:00:00), +Container (00:00:00), +market (00:00:00), +scan (00:00:00), +srcipt (00:00:00), +http (00:00:00), +sript (00:00:00), +srcipt (00:00:00), +sript (00:00:00)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-items (12:27:20.468), -} (12:27:40.523), -marker (12:36:09.957), -} (12:36:17.541), -; (12:38:00.710), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +market (00:00:00)</t>
+          <t>-items (12:27:20.468) ~0.80, -} (12:27:40.523), -marker (12:36:09.957) ~0.83, -} (12:36:17.541), -; (12:38:00.710), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +item (00:00:00), +market (00:00:00)</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -. (13:14:34.576), -( (13:14:36.285), -function (13:14:37.982), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
+          <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574) ~0.89, -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738) ~0.86, -startScanner (13:11:29.686) ~0.85, -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -. (13:14:34.576), -( (13:14:36.285), -function (13:14:37.982), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075) ~0.00, +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -script (12:52:45.286), -SCAN (13:00:21.378), -https (13:05:50.422), +positioning (00:00:00), +SCAn (00:00:00), +http (00:00:00), +srcipt (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -script (12:52:45.286) ~0.67, -SCAN (13:00:21.378) ~0.75, -https (13:05:50.422) ~0.80, +positioning (00:00:00), +SCAn (00:00:00), +http (00:00:00), +srcipt (00:00:00)</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Arial (12:27:44.328), -marker (12:36:09.957), -border (12:38:55.775), -; (12:42:02.654), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
+          <t>-Arial (12:27:44.328) ~0.83, -marker (12:36:09.957) ~0.83, -border (12:38:55.775) ~0.83, -; (12:42:02.654), +Artial (00:00:00), +market (00:00:00), +Border (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-showMarkerAt (13:20:05.930), +showMarketAt (00:00:00)</t>
+          <t>-showMarkerAt (13:20:05.930) ~0.92, +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>-environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
+          <t>-environment (13:12:42.232) ~0.91, -mapContainer (13:23:54.427) ~0.92, -mapContainer (13:24:12.088) ~0.92, +mapContainner (00:00:00), +mapContainner (00:00:00), +envitonment (00:00:00)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -onclick (12:59:42.303), +positioning (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +onClick (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -onclick (12:59:42.303) ~0.86, +positioning (00:00:00), +/ (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +onClick (00:00:00)</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -CANCEL (13:02:31.086), +( (00:00:00), +) (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innerText (00:00:00), +CANCEl (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -CANCEL (13:02:31.086) ~0.00, +( (00:00:00), +) (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innerText (00:00:00), +CANCEl (00:00:00), +; (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-! (12:19:34.144), -viewport (12:19:34.954), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -&gt; (12:19:35.534), -/ (12:19:35.634), -title (12:19:35.684), -QR (12:19:38.447), -/ (12:21:30.356), -QR (12:21:30.856), -stylesheet (12:23:47.522), -href (12:23:59.034), -toggleScanner (12:59:48.978), -&gt; (13:06:51.091), +veiwport (00:00:00), +OR (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +OR (00:00:00), +togglescanner (00:00:00)</t>
+          <t>-! (12:19:34.144), -viewport (12:19:34.954) ~0.75, -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -&gt; (12:19:35.534), -/ (12:19:35.634), -title (12:19:35.684), -QR (12:19:38.447), -/ (12:21:30.356), -QR (12:21:30.856) ~0.50, -stylesheet (12:23:47.522) ~0.80, -href (12:23:59.034) ~0.50, -toggleScanner (12:59:48.978) ~0.92, -&gt; (13:06:51.091) ~0.00, +veiwport (00:00:00), +OR (00:00:00), +sytlesheet (00:00:00), +herf (00:00:00), +OR (00:00:00), +togglescanner (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-# (12:41:14.043), -280 (12:41:14.808), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +green (00:00:00), +lime (00:00:00), +; (00:00:00)</t>
+          <t>-# (12:41:14.043), -280 (12:41:14.808) ~0.00, -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855) ~0.40, -) (12:42:30.228), -; (12:42:31.537) ~1.00, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +green (00:00:00), +lime (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-scannerOn (13:00:41.475), -CANCEL (13:02:31.086), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), +scannerON (00:00:00), +CANCLE (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
+          <t>-scannerOn (13:00:41.475) ~0.89, -CANCEL (13:02:31.086), -start (13:12:21.297) ~0.60, -environment (13:12:42.232) ~0.91, -showMarkerAt (13:20:05.930) ~0.92, +scannerON (00:00:00), +CANCLE (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-viewport (12:19:34.954), -png (12:30:36.357), +viewpoint (00:00:00), +PNG (00:00:00)</t>
+          <t>-viewport (12:19:34.954) ~0.78, -png (12:30:36.357) ~0.00, +viewpoint (00:00:00), +PNG (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-; (12:27:22.424), -} (12:32:35.009), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -# (12:36:08.726), -marker (12:36:09.957), -{ (12:36:10.360), -} (12:36:17.541), -width (12:36:18.827), -: (12:36:19.115), -3vw (12:36:23.573), -; (12:36:25.789), -height (12:37:16.574), -: (12:37:16.693), -3vw (12:37:18.454), -; (12:37:19.456), -background (12:37:29.322), -- (12:37:29.578), -color (12:37:30.642), -: (12:37:30.747), -black (12:37:31.976), -; (12:37:32.154), -border (12:37:58.210), -- (12:37:58.480), -radius (12:37:59.488), -: (12:37:59.684), -50 (12:38:00.274), -% (12:38:00.472), -; (12:38:00.710), -outline (12:38:33.154), -: (12:38:33.436), -5px (12:38:34.274), -solid (12:38:36.469), -border (12:38:55.775), -: (12:38:55.983), -5px (12:38:56.840), -solid (12:38:57.986), -white (12:38:59.153), -; (12:38:59.359), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -var (12:41:59.152), -( (12:41:59.354), -- (12:42:00.527), -theme (12:42:01.928), -) (12:42:02.226), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -position (12:44:00.909), -: (12:44:01.045), -absolute (12:44:03.220), -; (12:44:03.644), -top (12:44:05.651), -: (12:44:05.880), -0 (12:44:06.443), -; (12:44:06.772), -left (12:44:08.033), -: (12:44:08.227), -0 (12:44:08.691), -; (12:44:08.978), -transform (12:45:33.046), -: (12:45:33.314), -translate (12:45:34.855), -( (12:45:35.069), -- (12:45:35.321), -50 (12:45:35.855), -% (12:45:36.123), -, (12:45:36.383), -- (12:45:36.755), -50 (12:45:37.279), -% (12:45:37.687), -) (12:45:37.895), -; (12:45:38.251), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +# (00:00:00), +280 (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
+          <t>-; (12:27:22.424), -} (12:32:35.009), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -# (12:36:08.726), -marker (12:36:09.957), -{ (12:36:10.360), -} (12:36:17.541), -width (12:36:18.827), -: (12:36:19.115), -3vw (12:36:23.573), -; (12:36:25.789), -height (12:37:16.574), -: (12:37:16.693), -3vw (12:37:18.454), -; (12:37:19.456), -background (12:37:29.322) ~1.00, -- (12:37:29.578), -color (12:37:30.642), -: (12:37:30.747), -black (12:37:31.976), -; (12:37:32.154), -border (12:37:58.210), -- (12:37:58.480), -radius (12:37:59.488), -: (12:37:59.684), -50 (12:38:00.274), -% (12:38:00.472), -; (12:38:00.710), -outline (12:38:33.154), -: (12:38:33.436), -5px (12:38:34.274), -solid (12:38:36.469), -border (12:38:55.775), -: (12:38:55.983), -5px (12:38:56.840), -solid (12:38:57.986), -white (12:38:59.153), -; (12:38:59.359), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -var (12:41:59.152), -( (12:41:59.354), -- (12:42:00.527), -theme (12:42:01.928), -) (12:42:02.226) ~0.00, -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -position (12:44:00.909), -: (12:44:01.045), -absolute (12:44:03.220), -; (12:44:03.644), -top (12:44:05.651), -: (12:44:05.880), -0 (12:44:06.443), -; (12:44:06.772), -left (12:44:08.033), -: (12:44:08.227), -0 (12:44:08.691), -; (12:44:08.978), -transform (12:45:33.046), -: (12:45:33.314), -translate (12:45:34.855), -( (12:45:35.069), -- (12:45:35.321), -50 (12:45:35.855), -% (12:45:36.123), -, (12:45:36.383), -- (12:45:36.755), -50 (12:45:37.279), -% (12:45:37.687), -) (12:45:37.895), -; (12:45:38.251), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -# (13:08:25.754) ~1.00, -camera (13:08:26.947), -{ (13:08:27.300), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490) ~0.00, -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519), +# (00:00:00), +280 (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +red (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-showMarkerAt (12:56:12.525), -= (12:57:18.822), -" (13:02:31.386), -; (13:02:33.763), -" (13:02:39.256), -; (13:02:39.352), -, (13:13:22.080), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +; (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
+          <t>-showMarkerAt (12:56:12.525) ~0.92, -= (12:57:18.822), -" (13:02:31.386), -; (13:02:33.763), -" (13:02:39.256), -; (13:02:39.352), -, (13:13:22.080) ~0.00, -showMarkerAt (13:20:05.930) ~0.92, -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +; (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-/ (12:24:11.601), -onclick (12:59:42.303), +onClick (00:00:00)</t>
+          <t>-/ (12:24:11.601), -onclick (12:59:42.303) ~0.86, +onClick (00:00:00)</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -/ (12:24:11.601), +positioning (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -/ (12:24:11.601), +positioning (00:00:00)</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-startScanner (13:11:29.686), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +console (00:00:00), +log (00:00:00)</t>
+          <t>-startScanner (13:11:29.686) ~0.92, -const (13:19:51.277) ~0.57, -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262) ~0.00, -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), +startcanner (00:00:00), +console (00:00:00), +log (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>-/ (12:19:35.634), -&gt; (12:19:35.694), -QR (12:19:38.447), -Positioning (12:19:41.715), -&gt; (12:21:30.386), -QR (12:21:30.856), -Positioning (12:21:32.906), -&lt; (12:23:38.378), -link (12:23:39.280), -rel (12:23:45.117), -= (12:23:45.277), -" (12:23:45.703), -" (12:23:45.713), -stylesheet (12:23:47.522), -href (12:23:59.034), -= (12:23:59.297), -" (12:24:00.025), -" (12:24:00.035), -123456 (12:24:02.680), -. (12:24:02.918), -css (12:24:03.855), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -" (12:52:47.097), -&lt; (12:59:27.700), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), +OR (00:00:00), +positioning (00:00:00), +OR (00:00:00), +positioning (00:00:00), +body (00:00:00)</t>
+          <t>-/ (12:19:35.634), -&gt; (12:19:35.694), -QR (12:19:38.447) ~0.50, -Positioning (12:19:41.715) ~0.91, -&gt; (12:21:30.386), -QR (12:21:30.856) ~0.50, -Positioning (12:21:32.906) ~0.91, -&lt; (12:23:38.378), -link (12:23:39.280), -rel (12:23:45.117), -= (12:23:45.277), -" (12:23:45.703), -" (12:23:45.713), -stylesheet (12:23:47.522), -href (12:23:59.034), -= (12:23:59.297), -" (12:24:00.025), -" (12:24:00.035), -123456 (12:24:02.680), -. (12:24:02.918), -css (12:24:03.855), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -" (12:52:47.097), -&lt; (12:59:27.700), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), +OR (00:00:00), +positioning (00:00:00), +OR (00:00:00), +positioning (00:00:00), +body (00:00:00)</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-mapContainer (12:50:07.768), -none (13:24:50.402), +body (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +0 (00:00:00), +; (00:00:00), +column (00:00:00), +align (00:00:00), +mapcontainer (00:00:00)</t>
+          <t>-mapContainer (12:50:07.768) ~0.92, -none (13:24:50.402), +body (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +margin (00:00:00), +0 (00:00:00), +; (00:00:00), +column (00:00:00), +align (00:00:00), +mapcontainer (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>-showMarkerAt (12:56:12.525), -scannerOn (13:00:41.475), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -= (13:02:30.040), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -) (13:12:35.212), -facingMode (13:12:37.968), -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancel (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +showMarkeAT (00:00:00)</t>
+          <t>-showMarkerAt (12:56:12.525) ~0.83, -scannerOn (13:00:41.475) ~0.89, -scannerOn (13:02:03.160) ~0.89, -scannerOn (13:02:05.438) ~0.89, -scannerOn (13:02:26.202) ~0.89, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574) ~0.89, -= (13:02:30.040), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -} (13:02:36.228), -btn (13:02:36.869) ~0.17, -innerText (13:02:38.115) ~0.89, -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420) ~0.36, -) (13:12:35.212), -facingMode (13:12:37.968) ~0.80, -; (13:14:52.031), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -" (13:23:57.165), -none (13:23:57.811) ~0.33, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -block (13:24:16.075), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancel (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +showMarkeAT (00:00:00)</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>-stopScanner (13:15:09.792), +stopSCanner (00:00:00)</t>
+          <t>-stopScanner (13:15:09.792) ~0.91, +stopSCanner (00:00:00)</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-Positioning (12:19:41.715), -Positioning (12:21:32.906), -mapContainer (12:49:01.909), -toggleScanner (12:59:48.978), -SCAN (13:00:21.378), -https (13:05:50.422), -: (13:05:50.571), -html5 (13:05:54.075), -type (13:05:57.063), -text (13:06:02.121), -javascript (13:06:04.645), +positioning (00:00:00), +positioning (00:00:00), +mapcontainer (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +togglescanner (00:00:00), +scan (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), +123456 (00:00:00), +js (00:00:00), +&gt; (00:00:00), +script (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
+          <t>-Positioning (12:19:41.715) ~0.91, -Positioning (12:21:32.906) ~0.91, -mapContainer (12:49:01.909) ~0.92, -toggleScanner (12:59:48.978) ~0.92, -SCAN (13:00:21.378) ~0.00, -https (13:05:50.422) ~0.80, -: (13:05:50.571) ~0.00, -html5 (13:05:54.075) ~0.83, -type (13:05:57.063), -text (13:06:02.121), -javascript (13:06:04.645) ~0.20, +positioning (00:00:00), +positioning (00:00:00), +mapcontainer (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +togglescanner (00:00:00), +scan (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +src (00:00:00), +123456 (00:00:00), +js (00:00:00), +&gt; (00:00:00), +script (00:00:00), +http (00:00:00), +; (00:00:00), +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -scannerOn (13:00:41.475), -toggleScanner (13:02:00.332), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -startScanner (13:12:06.965), -; (13:14:52.031), -stopScanner (13:15:09.792), -toggleScanner (13:20:36.733), -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075), +scanneron (00:00:00), +togglescanner (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +mapcantainer (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancle (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +startscanner (00:00:00), +togglescanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.42, -marker (12:57:07.602) ~0.42, -scannerOn (13:00:41.475) ~0.89, -toggleScanner (13:02:00.332) ~0.92, -scannerOn (13:02:03.160) ~0.89, -scannerOn (13:02:05.438) ~0.89, -scannerOn (13:02:26.202) ~0.89, -btn (13:02:28.137) ~0.17, -innerText (13:02:29.574), -CANCEL (13:02:31.086), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -startScanner (13:12:06.965) ~0.92, -; (13:14:52.031), -stopScanner (13:15:09.792) ~0.91, -toggleScanner (13:20:36.733) ~0.92, -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088) ~0.92, -block (13:24:16.075) ~0.00, +scanneron (00:00:00), +togglescanner (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +mapcantainer (00:00:00), +. (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancle (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +startscanner (00:00:00), +togglescanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -Positioning (12:19:41.715), -html5 (13:05:54.075), +positioning (00:00:00), +html15 (00:00:00)</t>
+          <t>-! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -Positioning (12:19:41.715) ~0.91, -html5 (13:05:54.075) ~0.83, +positioning (00:00:00), +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-showMarkerAt (12:56:12.525), -startScanner (13:11:29.686), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), +StartScanner (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
+          <t>-showMarkerAt (12:56:12.525) ~0.92, -startScanner (13:11:29.686) ~0.92, -startScanner (13:12:06.965) ~0.92, -showMarkerAt (13:20:05.930) ~0.92, +StartScanner (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -marker (12:35:44.425), -toggleScanner (12:59:48.978), -html5 (13:05:54.075), +maker (00:00:00), +toggScanner (00:00:00), +html15 (00:00:00)</t>
+          <t>-- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -marker (12:35:44.425) ~0.83, -toggleScanner (12:59:48.978) ~0.85, -html5 (13:05:54.075) ~0.83, +maker (00:00:00), +toggScanner (00:00:00), +html15 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-; (12:32:37.955), -marker (12:36:09.957), -# (12:41:14.043), -280 (12:41:14.808), +green (00:00:00), +maker (00:00:00)</t>
+          <t>-; (12:32:37.955), -marker (12:36:09.957) ~0.83, -# (12:41:14.043), -280 (12:41:14.808) ~0.00, +green (00:00:00), +maker (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-marker (12:56:29.330), -marker (12:57:07.602), -left (12:57:18.355), -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612), -showMarkerAt (13:20:05.930), +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +maker (00:00:00), +maker (00:00:00), +top (00:00:00)</t>
+          <t>-marker (12:56:29.330) ~0.83, -marker (12:57:07.602) ~0.83, -left (12:57:18.355) ~0.00, -btn (13:02:28.137), -btn (13:02:36.869), -Html5Qrcode (13:09:48.612) ~0.64, -showMarkerAt (13:20:05.930) ~0.92, +HTML5QRcode (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +showmarkerAt (00:00:00), +maker (00:00:00), +maker (00:00:00), +top (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>-Html5Qrcode (13:09:48.612), +HTML5Qrcode (00:00:00)</t>
+          <t>-Html5Qrcode (13:09:48.612) ~0.73, +HTML5Qrcode (00:00:00)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-onclick (12:59:42.303), -toggleScanner (12:59:48.978), +" (00:00:00), +" (00:00:00), +onClick (00:00:00), +toogleScanner (00:00:00)</t>
+          <t>-onclick (12:59:42.303) ~0.86, -toggleScanner (12:59:48.978) ~0.92, +" (00:00:00), +" (00:00:00), +onClick (00:00:00), +toogleScanner (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-error (13:14:54.485), +log (00:00:00)</t>
+          <t>-error (13:14:54.485) ~0.20, +log (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-Positioning (12:21:32.906), -/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378), +Postitioning (00:00:00), +Scan (00:00:00)</t>
+          <t>-Positioning (12:21:32.906) ~0.92, -/ (12:24:11.601), -/ (12:29:22.840), -SCAN (13:00:21.378) ~0.25, +Postitioning (00:00:00), +Scan (00:00:00)</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-3vw (12:37:18.454), +3vh (00:00:00)</t>
+          <t>-3vw (12:37:18.454) ~0.67, +3vh (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-" (13:02:30.222), -CANCEL (13:02:31.086), -; (13:02:33.763), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -block (13:24:16.075), +Html5QRcode (00:00:00), +CANCLE (00:00:00), +SCANS (00:00:00)</t>
+          <t>-" (13:02:30.222), -CANCEL (13:02:31.086), -; (13:02:33.763), -SCAN (13:02:39.170) ~0.80, -" (13:02:39.256), -; (13:02:39.352), -Html5Qrcode (13:09:48.612) ~0.91, -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -block (13:24:16.075), +Html5QRcode (00:00:00), +CANCLE (00:00:00), +SCANS (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
